--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,720 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135121198</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>411723</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6971336</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135121200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>411716</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6971392</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135121201</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411511</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971343</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135121202</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411377</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6971319</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135121203</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411459</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971442</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135121204</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411502</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971381</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135121205</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411548</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971369</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1492,6 +1492,220 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135463143</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411617</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971368</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135463200</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411379</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87047809</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121198</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121200</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121201</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121202</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121203</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121204</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121205</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463143</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,8 +1755,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>135121198</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135121200</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>135121201</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>135121202</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>135121203</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>135121204</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135121205</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>135463143</v>
       </c>
       <c r="B10" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135463200</v>
       </c>
       <c r="B11" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1534,6 +1534,230 @@
       <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135121205</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135463143</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411617</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971368</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463143</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135463200</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411379</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463200</t>
         </is>
       </c>
     </row>
@@ -1547,6 +1771,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,45 +790,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135121198</v>
+        <v>135463143</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röverfallet, Hjd</t>
+          <t>A 25686-2026, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411723</v>
+        <v>411617</v>
       </c>
       <c r="R3" t="n">
-        <v>6971336</v>
+        <v>6971368</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,17 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,44 +887,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121198</t>
+          <t>https://artportalen.se/Sighting/135463143</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135121200</v>
+        <v>135463200</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103023</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -925,17 +932,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Röverfallet, Hjd</t>
+          <t>A 25686-2026, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411716</v>
+        <v>411379</v>
       </c>
       <c r="R4" t="n">
-        <v>6971392</v>
+        <v>6971387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,775 +997,16 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121200</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135121201</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>411511</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6971343</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121201</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>135121202</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>411377</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6971319</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121202</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>135121203</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>411459</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6971442</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121203</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>135121204</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>411502</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6971381</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121204</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>135121205</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>411548</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6971369</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121205</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>135463143</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57167</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>A 25686-2026, Hjd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>411617</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6971368</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135463143</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>135463200</v>
-      </c>
-      <c r="B11" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>103023</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tofsmes</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>A 25686-2026, Hjd</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>411379</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6971387</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463200</t>
         </is>
@@ -1766,13 +1017,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,57 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135463143</v>
+        <v>135121198</v>
       </c>
       <c r="B3" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 25686-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411617</v>
+        <v>411723</v>
       </c>
       <c r="R3" t="n">
-        <v>6971368</v>
+        <v>6971336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,12 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,44 +880,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463143</t>
+          <t>https://artportalen.se/Sighting/135121198</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135463200</v>
+        <v>135121200</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,25 +925,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 25686-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411379</v>
+        <v>411716</v>
       </c>
       <c r="R4" t="n">
-        <v>6971387</v>
+        <v>6971392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,12 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,16 +987,775 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135121201</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411511</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971343</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121201</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135121202</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411377</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6971319</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121202</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135121203</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411459</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971442</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121203</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135121204</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411502</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971381</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121204</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135121205</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411548</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971369</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121205</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135463143</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411617</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971368</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463143</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135463200</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411379</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463200</t>
         </is>
@@ -1017,6 +1766,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>135121198</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135121200</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>135121201</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>135121202</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>135121203</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>135121204</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135121205</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>135463143</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>135463200</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,45 +790,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135121198</v>
+        <v>135463143</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röverfallet, Hjd</t>
+          <t>A 25686-2026, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411723</v>
+        <v>411617</v>
       </c>
       <c r="R3" t="n">
-        <v>6971336</v>
+        <v>6971368</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,17 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,44 +887,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121198</t>
+          <t>https://artportalen.se/Sighting/135463143</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135121200</v>
+        <v>135463200</v>
       </c>
       <c r="B4" t="n">
-        <v>57982</v>
+        <v>58138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103023</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -925,17 +932,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Röverfallet, Hjd</t>
+          <t>A 25686-2026, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411716</v>
+        <v>411379</v>
       </c>
       <c r="R4" t="n">
-        <v>6971392</v>
+        <v>6971387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,775 +997,16 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121200</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135121201</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>411511</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6971343</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121201</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>135121202</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>411377</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6971319</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121202</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>135121203</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>411459</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6971442</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121203</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>135121204</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>411502</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6971381</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121204</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>135121205</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>411548</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6971369</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121205</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>135463143</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57169</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>A 25686-2026, Hjd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>411617</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6971368</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135463143</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>135463200</v>
-      </c>
-      <c r="B11" t="n">
-        <v>58138</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>103023</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tofsmes</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>A 25686-2026, Hjd</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>411379</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6971387</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463200</t>
         </is>
@@ -1766,13 +1017,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,57 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135463143</v>
+        <v>135121198</v>
       </c>
       <c r="B3" t="n">
-        <v>57169</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 25686-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411617</v>
+        <v>411723</v>
       </c>
       <c r="R3" t="n">
-        <v>6971368</v>
+        <v>6971336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,12 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,44 +880,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463143</t>
+          <t>https://artportalen.se/Sighting/135121198</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135463200</v>
+        <v>135121200</v>
       </c>
       <c r="B4" t="n">
-        <v>58138</v>
+        <v>57982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,25 +925,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 25686-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411379</v>
+        <v>411716</v>
       </c>
       <c r="R4" t="n">
-        <v>6971387</v>
+        <v>6971392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,12 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,16 +987,775 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135121201</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411511</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971343</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121201</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135121202</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411377</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6971319</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121202</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135121203</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411459</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971442</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121203</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135121204</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411502</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971381</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121204</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135121205</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411548</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971369</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121205</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135463143</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411617</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971368</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463143</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135463200</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411379</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463200</t>
         </is>
@@ -1017,6 +1766,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>135121198</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135121200</v>
       </c>
       <c r="B4" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>135121201</v>
       </c>
       <c r="B5" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>135121202</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>135121203</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>135121204</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135121205</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>135121198</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135121200</v>
       </c>
       <c r="B4" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>135121201</v>
       </c>
       <c r="B5" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>135121202</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>135121203</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>135121204</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135121205</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>135121198</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135121200</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>135121201</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>135121202</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>135121203</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>135121204</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135121205</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>135121198</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135121200</v>
       </c>
       <c r="B4" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>135121201</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>135121202</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>135121203</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>135121204</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135121205</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,45 +790,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135121198</v>
+        <v>135463143</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>57169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röverfallet, Hjd</t>
+          <t>A 25686-2026, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411723</v>
+        <v>411617</v>
       </c>
       <c r="R3" t="n">
-        <v>6971336</v>
+        <v>6971368</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,17 +867,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,44 +887,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121198</t>
+          <t>https://artportalen.se/Sighting/135463143</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135121200</v>
+        <v>135463200</v>
       </c>
       <c r="B4" t="n">
-        <v>57993</v>
+        <v>58138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103023</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -925,17 +932,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Röverfallet, Hjd</t>
+          <t>A 25686-2026, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411716</v>
+        <v>411379</v>
       </c>
       <c r="R4" t="n">
-        <v>6971392</v>
+        <v>6971387</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +977,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,775 +997,16 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121200</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135121201</v>
-      </c>
-      <c r="B5" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>411511</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6971343</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121201</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>135121202</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>411377</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6971319</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121202</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>135121203</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>411459</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6971442</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121203</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>135121204</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>411502</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6971381</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121204</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>135121205</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Röverfallet, Hjd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>411548</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6971369</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135121205</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>135463143</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57169</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>A 25686-2026, Hjd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>411617</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6971368</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135463143</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>135463200</v>
-      </c>
-      <c r="B11" t="n">
-        <v>58138</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>103023</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tofsmes</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>A 25686-2026, Hjd</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>411379</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6971387</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463200</t>
         </is>
@@ -1766,13 +1017,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25686-2026 artfynd.xlsx
+++ b/artfynd/A 25686-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,57 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135463143</v>
+        <v>135121198</v>
       </c>
       <c r="B3" t="n">
-        <v>57169</v>
+        <v>58006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 25686-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411617</v>
+        <v>411723</v>
       </c>
       <c r="R3" t="n">
-        <v>6971368</v>
+        <v>6971336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,12 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,44 +880,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463143</t>
+          <t>https://artportalen.se/Sighting/135121198</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135463200</v>
+        <v>135121200</v>
       </c>
       <c r="B4" t="n">
-        <v>58138</v>
+        <v>58006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103023</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,25 +925,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 25686-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411379</v>
+        <v>411716</v>
       </c>
       <c r="R4" t="n">
-        <v>6971387</v>
+        <v>6971392</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,12 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,16 +987,775 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135121201</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411511</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971343</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121201</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135121202</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411377</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6971319</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121202</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135121203</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411459</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971442</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121203</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135121204</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>411502</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971381</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121204</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135121205</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>411548</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971369</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121205</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135463143</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>411617</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971368</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463143</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135463200</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 25686-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411379</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463200</t>
         </is>
@@ -1017,6 +1766,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
